--- a/apps/web/public/importmallar/importmall-operationer.xlsx
+++ b/apps/web/public/importmallar/importmall-operationer.xlsx
@@ -46,7 +46,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obligatorisk. Resursens tresiffriga nummer i resursregistret (Tillverkning → Resurser) — resursen måste finnas. 1–2 siffror fylls på med nollor (7 blir 007). En legoresurs ger en lego-operation med tiderna 0.</t>
+          <t xml:space="preserve">Obligatorisk. Resursens tresiffriga nummer i resursregistret (Tillverkning → Resurser) — resursen måste finnas. 1–2 siffror fylls ut med nollor (7 blir 007). En legoresurs ger en lego-operation med tiderna 0.</t>
         </r>
       </text>
     </comment>
@@ -82,7 +82,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Enheten för Ställtid och Stycktid på raden: minuter/enhet (även min), antal/timme (även st/h — ställtiden då i timmar), timmar/enhet (även tim eller h) eller sekunder/enhet (även sek eller s). Tom cell betyder minuter; ett okänt ord ger ett fel. Lagringen är alltid minuter; antal/timme sparas med visningsenheten st/h.</t>
+          <t xml:space="preserve">Enheten för Ställtid och Stycktid på raden: minuter/enhet (även min), antal/timme (även st/h — ställtiden då i timmar), timmar/enhet (även tim eller h) eller sekunder/enhet (även sek eller s). Tom cell betyder minuter — även med Uppdatera befintliga operationer, där en befintlig operation då får tidsenheten minuter. Ett okänt ord ger ett fel. Lagringen är alltid minuter; antal/timme sparas med visningsenheten st/h.</t>
         </r>
       </text>
     </comment>
@@ -94,7 +94,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej. Ja gör operationen till en kalkyloperation som bara räknas i förkalkylen och aldrig frisläpps eller rapporteras.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej — även med Uppdatera befintliga operationer, där en befintlig kalkyloperation då blir en vanlig operation. Ja gör operationen till en kalkyloperation som bara räknas i förkalkylen och aldrig frisläpps eller rapporteras.</t>
         </r>
       </text>
     </comment>
@@ -173,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -182,6 +182,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -193,9 +194,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1" style="4"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1" style="4"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
@@ -290,66 +291,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artikelnummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Numret på en artikel som redan finns i artikelregistret. En artikel som inte är tillverkad importeras med en varning — operationen används inte vid tillverkning.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SB-1200</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sekvensnr</t>
+          <t xml:space="preserve">Artikelnummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -359,19 +345,19 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operationens ordningsnummer på artikeln, heltal större än 0 (t.ex. 10, 20, 30). Artikel + sekvensnr är nyckeln: finns operationen redan blir raden ett fel, hoppas över med Hoppa över rader som redan finns, eller skrivs över med Uppdatera befintliga operationer.</t>
+          <t xml:space="preserve">Numret på en artikel som redan finns i artikelregistret. En artikel som inte är tillverkad importeras med en varning — operationen används inte vid tillverkning.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">SB-1200</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resurs</t>
+          <t xml:space="preserve">Sekvensnr</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -381,19 +367,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resursens tresiffriga nummer i resursregistret (Tillverkning → Resurser) — resursen måste finnas. 1–2 siffror fylls på med nollor (7 blir 007). En legoresurs ger en lego-operation med tiderna 0.</t>
+          <t xml:space="preserve">Operationens ordningsnummer på artikeln, heltal större än 0 (t.ex. 10, 20, 30). Artikel + sekvensnr är nyckeln: finns operationen redan blir raden ett fel, hoppas över med Hoppa över rader som redan finns, eller skrivs över med Uppdatera befintliga operationer.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ställtid</t>
+          <t xml:space="preserve">Resurs</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -403,19 +389,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omställningstid per order i den enhet Tidsenhet anger — minuter när den kolumnen saknas eller är tom, timmar vid antal/timme. Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar ställtid; kolumnen måste finnas med.</t>
+          <t xml:space="preserve">Resursens tresiffriga nummer i resursregistret (Tillverkning → Resurser) — resursen måste finnas. 1–2 siffror fylls ut med nollor (7 blir 007). En legoresurs ger en lego-operation med tiderna 0.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">110</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stycktid</t>
+          <t xml:space="preserve">Ställtid</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -425,41 +411,41 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tid per styck i den enhet Tidsenhet anger — minuter per styck när den kolumnen saknas; vid antal/timme är värdet i stället antal styck per timme (360 blir 0,1667 min/st). Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar stycktid; kolumnen måste finnas med.</t>
+          <t xml:space="preserve">Omställningstid per order i den enhet Tidsenhet anger — minuter när den kolumnen saknas eller är tom, timmar vid antal/timme. Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar ställtid; kolumnen måste finnas med.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2,5</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tidsenhet</t>
+          <t xml:space="preserve">Stycktid</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enheten för Ställtid och Stycktid på raden: minuter/enhet (även min), antal/timme (även st/h — ställtiden då i timmar), timmar/enhet (även tim eller h) eller sekunder/enhet (även sek eller s). Tom cell betyder minuter; ett okänt ord ger ett fel. Lagringen är alltid minuter; antal/timme sparas med visningsenheten st/h.</t>
+          <t xml:space="preserve">Tid per styck i den enhet Tidsenhet anger — minuter per styck när den kolumnen saknas; vid antal/timme är värdet i stället antal styck per timme (360 blir 0,1667 min/st). Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar stycktid; kolumnen måste finnas med.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">minuter/enhet</t>
+          <t xml:space="preserve">2,5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalkyl</t>
+          <t xml:space="preserve">Tidsenhet</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -469,19 +455,19 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej. Ja gör operationen till en kalkyloperation som bara räknas i förkalkylen och aldrig frisläpps eller rapporteras.</t>
+          <t xml:space="preserve">Enheten för Ställtid och Stycktid på raden: minuter/enhet (även min), antal/timme (även st/h — ställtiden då i timmar), timmar/enhet (även tim eller h) eller sekunder/enhet (även sek eller s). Tom cell betyder minuter — även med Uppdatera befintliga operationer, där en befintlig operation då får tidsenheten minuter. Ett okänt ord ger ett fel. Lagringen är alltid minuter; antal/timme sparas med visningsenheten st/h.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">minuter/enhet</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kommentar</t>
+          <t xml:space="preserve">Kalkyl</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -491,19 +477,19 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operationens instruktionstext, max 1 000 tecken. Kryssrutan Skriv ut kommentaren på arbetskortet i guiden avgör om den skrivs ut på TO-utskriften. Tom cell lämnar en befintlig kommentar orörd vid uppdatering.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej — även med Uppdatera befintliga operationer, där en befintlig kalkyloperation då blir en vanlig operation. Ja gör operationen till en kalkyloperation som bara räknas i förkalkylen och aldrig frisläpps eller rapporteras.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kontrollera måtten mot ritningen före kantpressning</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beskrivning</t>
+          <t xml:space="preserve">Kommentar</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -513,32 +499,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operationens namn, max 255 tecken (t.ex. Kantpressning). Tom cell lämnar ett befintligt namn orört vid uppdatering.</t>
+          <t xml:space="preserve">Operationens instruktionstext, max 1 000 tecken. Kryssrutan Skriv ut kommentaren på arbetskortet i guiden avgör om den skrivs ut på TO-utskriften. Tom cell lämnar en befintlig kommentar orörd vid uppdatering.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laserskärning</t>
+          <t xml:space="preserve">Kontrollera måtten mot ritningen före kantpressning</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Beskrivning</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operationens namn, max 255 tecken (t.ex. Kantpressning). Tom cell lämnar ett befintligt namn orört vid uppdatering.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laserskärning</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Packinstruktion</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Packinstruktion för operationen, max 1 000 tecken. Tom cell lämnar en befintlig orörd vid uppdatering.</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mellanlägg av papp mellan varje enhet</t>
         </is>

--- a/apps/web/public/importmallar/importmall-operationer.xlsx
+++ b/apps/web/public/importmallar/importmall-operationer.xlsx
@@ -58,7 +58,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obligatorisk. Omställningstid per order i den enhet Tidsenhet anger — minuter när den kolumnen saknas eller är tom, timmar vid antal/timme. Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar ställtid; kolumnen måste finnas med.</t>
+          <t xml:space="preserve">Omställningstid per order i den enhet Tidsenhet anger — minuter när den kolumnen saknas eller är tom, timmar vid antal/timme. Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar ställtid — en rad på en vanlig resurs utan ställtid blir ett radfel. På en legoresurs sparas alltid 0, och kolumnen behövs inte.</t>
         </r>
       </text>
     </comment>
@@ -70,7 +70,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obligatorisk. Tid per styck i den enhet Tidsenhet anger — minuter per styck när den kolumnen saknas; vid antal/timme är värdet i stället antal styck per timme (360 blir 0,1667 min/st). Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar stycktid; kolumnen måste finnas med.</t>
+          <t xml:space="preserve">Tid per styck i den enhet Tidsenhet anger — minuter per styck när den kolumnen saknas; vid antal/timme är värdet i stället antal styck per timme (360 blir 0,1667 min/st). Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar stycktid — en rad på en vanlig resurs utan stycktid blir ett radfel. På en legoresurs sparas alltid 0, och kolumnen behövs inte.</t>
         </r>
       </text>
     </comment>
@@ -131,6 +131,54 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Packinstruktion för operationen, max 1 000 tecken. Tom cell lämnar en befintlig orörd vid uppdatering.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bara för operationer på en legoresurs: leverantören som utför arbetet. Måste finnas i leverantörsregistret. Tom cell ger legoresursens egen leverantör på en ny operation och lämnar en befintlig orörd. På en vanlig resurs ignoreras kolumnen med en varning.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bara för legooperationer: engångskostnaden per order i kronor. Decimalkomma eller punkt, aldrig negativ, högst 2 decimaler — fler avrundas med en varning. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bara för legooperationer: kostnaden per styck i kronor. Decimalkomma eller punkt, aldrig negativ, högst 4 decimaler — fler avrundas med en varning. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Operationens produktiva tid per styck, i samma enhet som Stycktid (Tidsenhet). Decimalkomma eller punkt, aldrig negativ; 0 betyder ingen cykeltid. Ignoreras på legoresurser. Tom cell lämnar fältet orört på en befintlig post.</t>
         </r>
       </text>
     </comment>
@@ -204,6 +252,10 @@
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1" style="4"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -255,6 +307,26 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Packinstruktion</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leverantör</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ställpris</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Styckpris</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cykeltid</t>
         </is>
       </c>
     </row>
@@ -406,12 +478,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omställningstid per order i den enhet Tidsenhet anger — minuter när den kolumnen saknas eller är tom, timmar vid antal/timme. Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar ställtid; kolumnen måste finnas med.</t>
+          <t xml:space="preserve">Omställningstid per order i den enhet Tidsenhet anger — minuter när den kolumnen saknas eller är tom, timmar vid antal/timme. Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar ställtid — en rad på en vanlig resurs utan ställtid blir ett radfel. På en legoresurs sparas alltid 0, och kolumnen behövs inte.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -428,12 +500,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tid per styck i den enhet Tidsenhet anger — minuter per styck när den kolumnen saknas; vid antal/timme är värdet i stället antal styck per timme (360 blir 0,1667 min/st). Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar stycktid; kolumnen måste finnas med.</t>
+          <t xml:space="preserve">Tid per styck i den enhet Tidsenhet anger — minuter per styck när den kolumnen saknas; vid antal/timme är värdet i stället antal styck per timme (360 blir 0,1667 min/st). Decimalkomma eller punkt, aldrig negativ. Skriv 0 när momentet saknar stycktid — en rad på en vanlig resurs utan stycktid blir ett radfel. På en legoresurs sparas alltid 0, och kolumnen behövs inte.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -549,6 +621,94 @@
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mellanlägg av papp mellan varje enhet</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leverantör</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bara för operationer på en legoresurs: leverantören som utför arbetet. Måste finnas i leverantörsregistret. Tom cell ger legoresursens egen leverantör på en ny operation och lämnar en befintlig orörd. På en vanlig resurs ignoreras kolumnen med en varning.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20015</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ställpris</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bara för legooperationer: engångskostnaden per order i kronor. Decimalkomma eller punkt, aldrig negativ, högst 2 decimaler — fler avrundas med en varning. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Styckpris</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bara för legooperationer: kostnaden per styck i kronor. Decimalkomma eller punkt, aldrig negativ, högst 4 decimaler — fler avrundas med en varning. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cykeltid</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operationens produktiva tid per styck, i samma enhet som Stycktid (Tidsenhet). Decimalkomma eller punkt, aldrig negativ; 0 betyder ingen cykeltid. Ignoreras på legoresurser. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,5</t>
         </is>
       </c>
     </row>

--- a/apps/web/public/importmallar/importmall-operationer.xlsx
+++ b/apps/web/public/importmallar/importmall-operationer.xlsx
@@ -171,6 +171,18 @@
       </text>
     </comment>
     <comment ref="N1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bara för legooperationer: frakten till och från leverantören i kronor, en gång per order. Decimalkomma eller punkt, aldrig negativ, högst 2 decimaler. Läggs ihop med ställpriset på legoinköpsordern och i kalkylen. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -255,7 +267,8 @@
     <col min="11" max="11" width="14" customWidth="1" style="4"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -325,6 +338,11 @@
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transportkostnad</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Cykeltid</t>
         </is>
@@ -693,20 +711,42 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Transportkostnad</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bara för legooperationer: frakten till och från leverantören i kronor, en gång per order. Decimalkomma eller punkt, aldrig negativ, högst 2 decimaler. Läggs ihop med ställpriset på legoinköpsordern och i kalkylen. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cykeltid</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Operationens produktiva tid per styck, i samma enhet som Stycktid (Tidsenhet). Decimalkomma eller punkt, aldrig negativ; 0 betyder ingen cykeltid. Ignoreras på legoresurser. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,5</t>
         </is>

--- a/apps/web/public/importmallar/importmall-operationer.xlsx
+++ b/apps/web/public/importmallar/importmall-operationer.xlsx
@@ -82,7 +82,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Enheten för Ställtid och Stycktid på raden: minuter/enhet (även min), antal/timme (även st/h — ställtiden då i timmar), timmar/enhet (även tim eller h) eller sekunder/enhet (även sek eller s). Tom cell betyder minuter — även med Uppdatera befintliga operationer, där en befintlig operation då får tidsenheten minuter. Ett okänt ord ger ett fel. Lagringen är alltid minuter; antal/timme sparas med visningsenheten st/h.</t>
+          <t xml:space="preserve">Enheten för Ställtid och Stycktid på raden: minuter/enhet (även min), antal/timme (även st/h — ställtiden då i timmar), timmar/enhet (även tim eller h) eller sekunder/enhet (även sek eller s). Tom cell betyder minuter — även med Uppdatera befintliga operationer, där en befintlig operation då får tidsenheten minuter. Ett okänt ord ger ett fel. Lagringen är alltid minuter; antal/timme sparas med visningsenheten st/h och sekunder/enhet med sek/st.</t>
         </r>
       </text>
     </comment>
@@ -545,7 +545,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enheten för Ställtid och Stycktid på raden: minuter/enhet (även min), antal/timme (även st/h — ställtiden då i timmar), timmar/enhet (även tim eller h) eller sekunder/enhet (även sek eller s). Tom cell betyder minuter — även med Uppdatera befintliga operationer, där en befintlig operation då får tidsenheten minuter. Ett okänt ord ger ett fel. Lagringen är alltid minuter; antal/timme sparas med visningsenheten st/h.</t>
+          <t xml:space="preserve">Enheten för Ställtid och Stycktid på raden: minuter/enhet (även min), antal/timme (även st/h — ställtiden då i timmar), timmar/enhet (även tim eller h) eller sekunder/enhet (även sek eller s). Tom cell betyder minuter — även med Uppdatera befintliga operationer, där en befintlig operation då får tidsenheten minuter. Ett okänt ord ger ett fel. Lagringen är alltid minuter; antal/timme sparas med visningsenheten st/h och sekunder/enhet med sek/st.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
